--- a/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
+++ b/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
@@ -2725,12 +2725,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>`FST-409`</t>
+          <t>`STI-403`</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Manajemen Sains &amp; Riset Op</t>
+          <t>Pengantar NLP &amp; IR</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -2739,22 +2739,22 @@
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>**R**</t>
-        </is>
-      </c>
+      <c r="F49" s="8" t="inlineStr"/>
       <c r="G49" s="8" t="inlineStr"/>
       <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>**R**</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr"/>
       <c r="K49" s="8" t="inlineStr"/>
       <c r="L49" s="8" t="inlineStr"/>
-      <c r="M49" s="8" t="inlineStr"/>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>**R**</t>
+        </is>
+      </c>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="8" t="inlineStr"/>
       <c r="P49" s="8" t="inlineStr"/>
@@ -2762,12 +2762,12 @@
       <c r="R49" s="8" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>PL-1, PL-4</t>
+          <t>PL-1</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>PEO-1, PEO-2</t>
+          <t>PEO-1, PEO-3</t>
         </is>
       </c>
       <c r="U49" s="8" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>`STI-102`, `STI-103`, `STI-201`, `STI-202`, `FST-408`, `FST-409`</t>
+          <t>`STI-102`, `STI-103`, `STI-201`, `STI-202`, `FST-408`</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>7 MK</t>
+          <t>6 MK</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-601`, `STA-03`, `STA-05`</t>
+          <t>`STI-302`, `STI-403`, `STI-601`, `STA-03`, `STA-05`</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>6 MK</t>
+          <t>7 MK</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-401`, `STI-501`, `STI-601`</t>
+          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>8 MK</t>
+          <t>9 MK</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>`FST-409`</t>
+          <t>`STI-403`</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Manajemen Sains &amp; Riset Op</t>
+          <t>Pengantar NLP &amp; IR</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
@@ -8721,22 +8721,22 @@
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="H196" s="8" t="inlineStr">
         <is>
-          <t>**50%**</t>
+          <t>**65%**</t>
         </is>
       </c>
       <c r="I196" s="8" t="inlineStr">

--- a/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
+++ b/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
@@ -562,7 +562,7 @@
     <col width="28.75" customWidth="1" min="6" max="6"/>
     <col width="37.95" customWidth="1" min="7" max="7"/>
     <col width="37.95" customWidth="1" min="8" max="8"/>
-    <col width="25.3" customWidth="1" min="9" max="9"/>
+    <col width="32.2" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Logika Informatika</t>
+          <t>Arsitektur &amp; Org. Sistem TI</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1190,7 +1190,11 @@
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>**I**</t>
+        </is>
+      </c>
       <c r="L21" s="7" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
@@ -1392,7 +1396,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Matematika Diskrit</t>
+          <t>Matematika Diskrit &amp; Logika</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1401,7 +1405,11 @@
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>**I**</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
@@ -6248,7 +6256,7 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-404`, `STI-305`</t>
+          <t>`STI-103`, `STI-307`, `STI-404`, `STI-305`</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
@@ -6258,7 +6266,7 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>6 MK</t>
+          <t>7 MK</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -6472,7 +6480,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>`STI-102`, `STI-103`, `STI-201`, `STI-202`, `FST-408`</t>
+          <t>`STI-102`, `STI-201`, `STI-202`, `FST-408`</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -6482,7 +6490,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>6 MK</t>
+          <t>5 MK</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -7536,7 +7544,7 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>Logika Informatika</t>
+          <t>Arsitektur &amp; Org. Sistem TI</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
@@ -7566,7 +7574,7 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>*MK Teori Dasar Sains*</t>
+          <t>*MK Teori Sistem &amp; Hardware*</t>
         </is>
       </c>
     </row>
@@ -7593,27 +7601,27 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>**60%**</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>✅ Patuh IKU 7</t>
+          <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
@@ -7640,27 +7648,27 @@
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>**60%**</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>✅ Patuh IKU 7</t>
+          <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
@@ -7687,27 +7695,27 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>**60%**</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>✅ Patuh IKU 7</t>
+          <t>*MK Keterampilan Komunikasi*</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7732,7 @@
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>Matematika Diskrit</t>
+          <t>Matematika Diskrit &amp; Logika</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">

--- a/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
+++ b/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U220"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -6138,7 +6138,7 @@
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TABEL 6.1: PEMETAAN 19 BAHAN KAJIAN IS2020 (APTIKOM v2.0) ↔ MATA KULIAH</t>
+          <t>TABEL 6.1: PEMETAAN 21 BAHAN KAJIAN IS2020 (APTIKOM v2.0) ↔ MATA KULIAH</t>
         </is>
       </c>
       <c r="B126" s="4" t="n"/>
@@ -6787,139 +6787,139 @@
         </is>
       </c>
     </row>
-    <row r="147"/>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>TABEL 6.2: PEMETAAN 14 BAHAN KAJIAN UTAMA IT2017 (APTIKOM) ↔ MATA KULIAH</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="n"/>
-      <c r="C148" s="4" t="n"/>
-      <c r="D148" s="4" t="n"/>
-      <c r="E148" s="4" t="n"/>
-      <c r="F148" s="5" t="n"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>**BK-IS20**</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>*Ethics, Use and Implications for Society*</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>`STI-405`, `STI-602`, `STB-04`</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>4 MK</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>**BK-IS21**</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>*Internship and Professional Practice*</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>`FST-612`</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>`MKU-507`, `FST-610`</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>3 MK</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149"/>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>TABEL 6.2: PEMETAAN 15 BAHAN KAJIAN UTAMA IT2017 (APTIKOM) ↔ MATA KULIAH</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="5" t="n"/>
+    </row>
+    <row r="151" ht="26" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>Kode BoK IT</t>
         </is>
       </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>Nomenklatur Bahan Kajian Utama IT2017</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>Mata Kuliah Pembina Primer (●)</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>Mata Kuliah Pembina Sekunder (○)</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E151" s="6" t="inlineStr">
         <is>
           <t>Total MK</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <t>Status Cakupan</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>**BK-IT01**</t>
-        </is>
-      </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>*Information Technology Fundamentals*</t>
-        </is>
-      </c>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>`FST-101`, `STI-101`</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>`FST-204`</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>3 MK</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>✅ Sangat Kuat</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>**BK-IT02**</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="inlineStr">
-        <is>
-          <t>*Applied AI &amp; Intelligent Technologies*</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
-        </is>
-      </c>
-      <c r="D151" s="8" t="inlineStr">
-        <is>
-          <t>`STA-03..06`</t>
-        </is>
-      </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t>9 MK</t>
-        </is>
-      </c>
-      <c r="F151" s="8" t="inlineStr">
-        <is>
-          <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>**BK-IT03**</t>
+          <t>**BK-IT01**</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>*Networking &amp; Communications*</t>
+          <t>*Information Technology Fundamentals*</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`FST-101`, `STI-101`</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`, `STI-504`, `STB-01`</t>
+          <t>`FST-204`</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>3 MK</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -6931,27 +6931,27 @@
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT04**</t>
+          <t>**BK-IT02**</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>*Platform Technologies &amp; Web/Mobile*</t>
+          <t>*Applied AI &amp; Intelligent Technologies*</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>`STC-03..05`</t>
+          <t>`STA-03..06`</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>7 MK</t>
+          <t>9 MK</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
@@ -6963,22 +6963,22 @@
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>**BK-IT05**</t>
+          <t>**BK-IT03**</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>*Cloud Computing &amp; Virtualization*</t>
+          <t>*Networking &amp; Communications*</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`, `STB-02`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>`STI-305`, `STC-05`</t>
+          <t>`STI-404`, `STI-504`, `STB-01`</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -6995,27 +6995,27 @@
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT06**</t>
+          <t>**BK-IT04**</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>*Cybersecurity Principles &amp; Defense*</t>
+          <t>*Platform Technologies &amp; Web/Mobile*</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-603`, `STB-01`</t>
-        </is>
-      </c>
-      <c r="D155" s="10" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>`STC-03..05`</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>7 MK</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -7027,27 +7027,27 @@
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>**BK-IT07**</t>
+          <t>**BK-IT05**</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>*System Integration and Architecture*</t>
+          <t>*Cloud Computing &amp; Virtualization*</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>`STI-601`, `STI-604`, `FST-610`</t>
+          <t>`STI-404`, `STB-02`</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>`STB-06`, `STC-02`</t>
+          <t>`STI-305`, `STC-05`</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>5 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
@@ -7059,59 +7059,59 @@
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT08**</t>
+          <t>**BK-IT06**</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>*IT Service Management &amp; Governance*</t>
+          <t>*Cybersecurity Principles &amp; Defense*</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>`STB-04`, `STB-05`</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr">
-        <is>
-          <t>`STI-506`</t>
+          <t>`STI-405`, `STI-603`, `STB-01`</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>`STB-03`</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>3 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>✅ Terpenuhi</t>
+          <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>**BK-IT09**</t>
+          <t>**BK-IT07**</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>*Data Analytics &amp; Information Visualization*</t>
+          <t>*System Integration and Architecture*</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>`STI-402`, `STI-503`</t>
+          <t>`STI-601`, `STI-604`, `FST-610`</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>`STA-01`, `STA-04`</t>
+          <t>`STB-06`, `STC-02`</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>5 MK</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -7123,59 +7123,59 @@
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT10**</t>
+          <t>**BK-IT08**</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>*User Experience &amp; Interaction Design*</t>
+          <t>*IT Service Management &amp; Governance*</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>`STI-303`, `STC-01`</t>
+          <t>`STB-04`, `STB-05`</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`, `STC-04`</t>
+          <t>`STI-506`</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>3 MK</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>✅ Sangat Kuat</t>
+          <t>✅ Terpenuhi</t>
         </is>
       </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>**BK-IT11**</t>
+          <t>**BK-IT09**</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>*Software Development Practices*</t>
+          <t>*Data Analytics &amp; Information Visualization*</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>`STI-304`, `STI-407`, `STI-604`</t>
+          <t>`STI-402`, `STI-503`</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>`FST-205`, `STC-05`</t>
+          <t>`STA-01`, `STA-04`</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>5 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
@@ -7187,59 +7187,59 @@
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT12**</t>
+          <t>**BK-IT10**</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>*IT Risk Management and Compliance*</t>
+          <t>*User Experience &amp; Interaction Design*</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>`STB-03`, `STB-04`</t>
+          <t>`STI-303`, `STC-01`</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>`FST-206`</t>
+          <t>`STI-306`, `STC-04`</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>3 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>✅ Terpenuhi</t>
+          <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>**BK-IT13**</t>
+          <t>**BK-IT11**</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>*Technology Entrepreneurship*</t>
+          <t>*Software Development Practices*</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>`MKU-204`, `STI-701`, `FST-610`</t>
-        </is>
-      </c>
-      <c r="D162" s="9" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+          <t>`STI-304`, `STI-407`, `STI-604`</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>`FST-205`, `STC-05`</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>5 MK</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
@@ -7251,2631 +7251,2727 @@
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
+          <t>**BK-IT12**</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>*IT Risk Management and Compliance*</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>`STB-03`, `STB-04`</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>3 MK</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>**BK-IT13**</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>*Technology Entrepreneurship*</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>`MKU-204`, `STI-701`, `FST-610`</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>`STC-06`</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>4 MK</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>✅ Sangat Kuat</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
           <t>**BK-IT14**</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>*IoT and Embedded Smart Systems*</t>
         </is>
       </c>
-      <c r="C163" s="8" t="inlineStr">
+      <c r="C165" s="8" t="inlineStr">
         <is>
           <t>`STI-504`, `STA-06`</t>
         </is>
       </c>
-      <c r="D163" s="8" t="inlineStr">
+      <c r="D165" s="8" t="inlineStr">
         <is>
           <t>`STI-305`, `STI-307`</t>
         </is>
       </c>
-      <c r="E163" s="8" t="inlineStr">
+      <c r="E165" s="8" t="inlineStr">
         <is>
           <t>4 MK</t>
         </is>
       </c>
-      <c r="F163" s="8" t="inlineStr">
+      <c r="F165" s="8" t="inlineStr">
         <is>
           <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
-    <row r="164"/>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="3" t="inlineStr">
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>**BK-IT15**</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>*Global Professional Practice*</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>`FST-205`, `FST-612`</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>`FST-206`, `MKU-507`</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>4 MK</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="167"/>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>7. MATRIKS KEPATUHAN IKU 7 &amp; METODE PEMBELAJARAN PARTISIPATIF PER MATA KULIAH</t>
         </is>
       </c>
-      <c r="B165" s="4" t="n"/>
-      <c r="C165" s="4" t="n"/>
-      <c r="D165" s="4" t="n"/>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="4" t="n"/>
-      <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="n"/>
-      <c r="I165" s="5" t="n"/>
-    </row>
-    <row r="166" ht="26" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
+      <c r="B168" s="4" t="n"/>
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="n"/>
+      <c r="E168" s="4" t="n"/>
+      <c r="F168" s="4" t="n"/>
+      <c r="G168" s="4" t="n"/>
+      <c r="H168" s="4" t="n"/>
+      <c r="I168" s="5" t="n"/>
+    </row>
+    <row r="169" ht="26" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>Kode MK</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>Nama Mata Kuliah</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>SKS</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E169" s="6" t="inlineStr">
         <is>
           <t>Bobot Case Method (%)</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <t>Bobot Team-Based PjBL (%)</t>
         </is>
       </c>
-      <c r="G166" s="6" t="inlineStr">
+      <c r="G169" s="6" t="inlineStr">
         <is>
           <t>Bobot Evaluasi Kognitif / Lab (%)</t>
         </is>
       </c>
-      <c r="H166" s="6" t="inlineStr">
+      <c r="H169" s="6" t="inlineStr">
         <is>
           <t>**Total Bobot IKU 7 (CM + PjBL)**</t>
         </is>
       </c>
-      <c r="I166" s="6" t="inlineStr">
+      <c r="I169" s="6" t="inlineStr">
         <is>
           <t>Status Kepatuhan IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="9" t="inlineStr">
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="B170" s="7" t="inlineStr">
         <is>
           <t>`FST-101`</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
+      <c r="C170" s="7" t="inlineStr">
         <is>
           <t>Dasar Teknologi Digital</t>
         </is>
       </c>
-      <c r="D167" s="9" t="inlineStr">
+      <c r="D170" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E167" s="7" t="inlineStr">
+      <c r="E170" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="F170" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="G170" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H167" s="7" t="inlineStr">
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>**50%**</t>
         </is>
       </c>
-      <c r="I167" s="7" t="inlineStr">
+      <c r="I170" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="10" t="inlineStr">
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>`FST-102`</t>
         </is>
       </c>
-      <c r="C168" s="8" t="inlineStr">
+      <c r="C171" s="8" t="inlineStr">
         <is>
           <t>Algoritma &amp; Pemrograman</t>
         </is>
       </c>
-      <c r="D168" s="10" t="inlineStr">
+      <c r="D171" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E168" s="8" t="inlineStr">
+      <c r="E171" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F168" s="8" t="inlineStr">
+      <c r="F171" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G168" s="8" t="inlineStr">
+      <c r="G171" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H168" s="8" t="inlineStr">
+      <c r="H171" s="8" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I168" s="8" t="inlineStr">
+      <c r="I171" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="9" t="inlineStr">
+    <row r="172" ht="16" customHeight="1">
+      <c r="A172" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B169" s="7" t="inlineStr">
+      <c r="B172" s="7" t="inlineStr">
         <is>
           <t>`STI-101`</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr">
+      <c r="C172" s="7" t="inlineStr">
         <is>
           <t>Pengantar Sistem &amp; TI</t>
         </is>
       </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E169" s="7" t="inlineStr">
+      <c r="E172" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G169" s="7" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H169" s="7" t="inlineStr">
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>**50%**</t>
         </is>
       </c>
-      <c r="I169" s="7" t="inlineStr">
+      <c r="I172" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="10" t="inlineStr">
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>`STI-102`</t>
         </is>
       </c>
-      <c r="C170" s="10" t="inlineStr">
+      <c r="C173" s="10" t="inlineStr">
         <is>
           <t>Kalkulus</t>
         </is>
       </c>
-      <c r="D170" s="10" t="inlineStr">
+      <c r="D173" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E170" s="8" t="inlineStr">
+      <c r="E173" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F170" s="8" t="inlineStr">
+      <c r="F173" s="8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G170" s="8" t="inlineStr">
+      <c r="G173" s="8" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H170" s="8" t="inlineStr">
+      <c r="H173" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I170" s="8" t="inlineStr">
+      <c r="I173" s="8" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="9" t="inlineStr">
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
         <is>
           <t>`STI-103`</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr">
+      <c r="C174" s="7" t="inlineStr">
         <is>
           <t>Arsitektur &amp; Org. Sistem TI</t>
         </is>
       </c>
-      <c r="D171" s="9" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E171" s="7" t="inlineStr">
+      <c r="E174" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="F174" s="7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H171" s="7" t="inlineStr">
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I171" s="7" t="inlineStr">
+      <c r="I174" s="7" t="inlineStr">
         <is>
           <t>*MK Teori Sistem &amp; Hardware*</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="10" t="inlineStr">
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>`MKU-101`</t>
         </is>
       </c>
-      <c r="C172" s="10" t="inlineStr">
+      <c r="C175" s="10" t="inlineStr">
         <is>
           <t>Agama I</t>
         </is>
       </c>
-      <c r="D172" s="10" t="inlineStr">
+      <c r="D175" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E172" s="8" t="inlineStr">
+      <c r="E175" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F172" s="8" t="inlineStr">
+      <c r="F175" s="8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G172" s="8" t="inlineStr">
+      <c r="G175" s="8" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H172" s="8" t="inlineStr">
+      <c r="H175" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="I175" s="8" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="9" t="inlineStr">
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B176" s="7" t="inlineStr">
         <is>
           <t>`MKU-102`</t>
         </is>
       </c>
-      <c r="C173" s="7" t="inlineStr">
+      <c r="C176" s="7" t="inlineStr">
         <is>
           <t>Pancasila</t>
         </is>
       </c>
-      <c r="D173" s="9" t="inlineStr">
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F176" s="7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H173" s="7" t="inlineStr">
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I173" s="7" t="inlineStr">
+      <c r="I176" s="7" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="10" t="inlineStr">
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>`MKU-103`</t>
         </is>
       </c>
-      <c r="C174" s="8" t="inlineStr">
+      <c r="C177" s="8" t="inlineStr">
         <is>
           <t>Bahasa Indonesia</t>
         </is>
       </c>
-      <c r="D174" s="10" t="inlineStr">
+      <c r="D177" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E174" s="8" t="inlineStr">
+      <c r="E177" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F174" s="8" t="inlineStr">
+      <c r="F177" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G174" s="8" t="inlineStr">
+      <c r="G177" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H174" s="8" t="inlineStr">
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="I177" s="8" t="inlineStr">
         <is>
           <t>*MK Keterampilan Komunikasi*</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="9" t="inlineStr">
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>`STI-201`</t>
         </is>
       </c>
-      <c r="C175" s="7" t="inlineStr">
+      <c r="C178" s="7" t="inlineStr">
         <is>
           <t>Matematika Diskrit &amp; Logika</t>
         </is>
       </c>
-      <c r="D175" s="9" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E175" s="7" t="inlineStr">
+      <c r="E178" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G175" s="7" t="inlineStr">
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H175" s="7" t="inlineStr">
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I175" s="7" t="inlineStr">
+      <c r="I178" s="7" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="10" t="inlineStr">
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>`STI-202`</t>
         </is>
       </c>
-      <c r="C176" s="8" t="inlineStr">
+      <c r="C179" s="8" t="inlineStr">
         <is>
           <t>Aljabar Linear &amp; Matriks</t>
         </is>
       </c>
-      <c r="D176" s="10" t="inlineStr">
+      <c r="D179" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
+      <c r="F179" s="8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G176" s="8" t="inlineStr">
+      <c r="G179" s="8" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H176" s="8" t="inlineStr">
+      <c r="H179" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I176" s="8" t="inlineStr">
+      <c r="I179" s="8" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="9" t="inlineStr">
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t>`FST-203`</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>Struktur Data &amp; Algoritma</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G177" s="7" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H177" s="7" t="inlineStr">
+      <c r="H180" s="7" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I177" s="7" t="inlineStr">
+      <c r="I180" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="10" t="inlineStr">
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>`FST-204`</t>
         </is>
       </c>
-      <c r="C178" s="8" t="inlineStr">
+      <c r="C181" s="8" t="inlineStr">
         <is>
           <t>Organisasi &amp; Arsitektur Kom</t>
         </is>
       </c>
-      <c r="D178" s="10" t="inlineStr">
+      <c r="D181" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E178" s="8" t="inlineStr">
+      <c r="E181" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F178" s="8" t="inlineStr">
+      <c r="F181" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G178" s="8" t="inlineStr">
+      <c r="G181" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H178" s="8" t="inlineStr">
+      <c r="H181" s="8" t="inlineStr">
         <is>
           <t>**50%**</t>
         </is>
       </c>
-      <c r="I178" s="8" t="inlineStr">
+      <c r="I181" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="9" t="inlineStr">
+    <row r="182" ht="16" customHeight="1">
+      <c r="A182" s="9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t>`FST-205`</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr">
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>Pemrograman Lanjut (OOP)</t>
         </is>
       </c>
-      <c r="D179" s="9" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H179" s="7" t="inlineStr">
+      <c r="H182" s="7" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I179" s="7" t="inlineStr">
+      <c r="I182" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="10" t="inlineStr">
+    <row r="183" ht="16" customHeight="1">
+      <c r="A183" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>`FST-206`</t>
         </is>
       </c>
-      <c r="C180" s="8" t="inlineStr">
+      <c r="C183" s="8" t="inlineStr">
         <is>
           <t>Etika Profesi &amp; Hukum Dig.</t>
         </is>
       </c>
-      <c r="D180" s="10" t="inlineStr">
+      <c r="D183" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
+      <c r="E183" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="F180" s="8" t="inlineStr">
+      <c r="F183" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G180" s="8" t="inlineStr">
+      <c r="G183" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H180" s="8" t="inlineStr">
+      <c r="H183" s="8" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I180" s="8" t="inlineStr">
+      <c r="I183" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="9" t="inlineStr">
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="B184" s="7" t="inlineStr">
         <is>
           <t>`FST-207`</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr">
+      <c r="C184" s="7" t="inlineStr">
         <is>
           <t>Sistem Basis Data</t>
         </is>
       </c>
-      <c r="D181" s="9" t="inlineStr">
+      <c r="D184" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E181" s="7" t="inlineStr">
+      <c r="E184" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
+      <c r="F184" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G181" s="7" t="inlineStr">
+      <c r="G184" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H181" s="7" t="inlineStr">
+      <c r="H184" s="7" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I181" s="7" t="inlineStr">
+      <c r="I184" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="10" t="inlineStr">
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>`MKU-204`</t>
         </is>
       </c>
-      <c r="C182" s="8" t="inlineStr">
+      <c r="C185" s="8" t="inlineStr">
         <is>
           <t>Kewirausahaan I</t>
         </is>
       </c>
-      <c r="D182" s="10" t="inlineStr">
+      <c r="D185" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E182" s="8" t="inlineStr">
+      <c r="E185" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F182" s="8" t="inlineStr">
+      <c r="F185" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G182" s="8" t="inlineStr">
+      <c r="G185" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H182" s="8" t="inlineStr">
+      <c r="H185" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="I185" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="9" t="inlineStr">
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B183" s="7" t="inlineStr">
+      <c r="B186" s="7" t="inlineStr">
         <is>
           <t>`STI-301`</t>
         </is>
       </c>
-      <c r="C183" s="7" t="inlineStr">
+      <c r="C186" s="7" t="inlineStr">
         <is>
           <t>Analisis &amp; Perancangan SI</t>
         </is>
       </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E183" s="7" t="inlineStr">
+      <c r="E186" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F183" s="7" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G183" s="7" t="inlineStr">
+      <c r="G186" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H183" s="7" t="inlineStr">
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I183" s="7" t="inlineStr">
+      <c r="I186" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="10" t="inlineStr">
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>`STI-302`</t>
         </is>
       </c>
-      <c r="C184" s="8" t="inlineStr">
+      <c r="C187" s="8" t="inlineStr">
         <is>
           <t>Sistem Cerdas</t>
         </is>
       </c>
-      <c r="D184" s="10" t="inlineStr">
+      <c r="D187" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E184" s="8" t="inlineStr">
+      <c r="E187" s="8" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F184" s="8" t="inlineStr">
+      <c r="F187" s="8" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G184" s="8" t="inlineStr">
+      <c r="G187" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H184" s="8" t="inlineStr">
+      <c r="H187" s="8" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I184" s="8" t="inlineStr">
+      <c r="I187" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t>`STI-303`</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
+      <c r="C188" s="7" t="inlineStr">
         <is>
           <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
-      <c r="D185" s="9" t="inlineStr">
+      <c r="D188" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="E188" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I185" s="7" t="inlineStr">
+      <c r="I188" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="10" t="inlineStr">
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>`STI-304`</t>
         </is>
       </c>
-      <c r="C186" s="8" t="inlineStr">
+      <c r="C189" s="8" t="inlineStr">
         <is>
           <t>Rekayasa Perangkat Lunak</t>
         </is>
       </c>
-      <c r="D186" s="10" t="inlineStr">
+      <c r="D189" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E186" s="8" t="inlineStr">
+      <c r="E189" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F186" s="8" t="inlineStr">
+      <c r="F189" s="8" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G186" s="8" t="inlineStr">
+      <c r="G189" s="8" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H186" s="8" t="inlineStr">
+      <c r="H189" s="8" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I186" s="8" t="inlineStr">
+      <c r="I189" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="9" t="inlineStr">
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>`STI-305`</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr">
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>Sistem Operasi</t>
         </is>
       </c>
-      <c r="D187" s="9" t="inlineStr">
+      <c r="D190" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E187" s="7" t="inlineStr">
+      <c r="E190" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
+      <c r="F190" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G187" s="7" t="inlineStr">
+      <c r="G190" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="H190" s="7" t="inlineStr">
         <is>
           <t>**55%**</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr">
+      <c r="I190" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="10" t="inlineStr">
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" s="10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>`STI-306`</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
+      <c r="C191" s="8" t="inlineStr">
         <is>
           <t>Web Front End Development</t>
         </is>
       </c>
-      <c r="D188" s="10" t="inlineStr">
+      <c r="D191" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E188" s="8" t="inlineStr">
+      <c r="E191" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F188" s="8" t="inlineStr">
+      <c r="F191" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G188" s="8" t="inlineStr">
+      <c r="G191" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H188" s="8" t="inlineStr">
+      <c r="H191" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="I191" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="16" customHeight="1">
-      <c r="A189" s="9" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t>`STI-307`</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr">
+      <c r="C192" s="7" t="inlineStr">
         <is>
           <t>Jaringan Komputer</t>
         </is>
       </c>
-      <c r="D189" s="9" t="inlineStr">
+      <c r="D192" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E189" s="7" t="inlineStr">
+      <c r="E192" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F189" s="7" t="inlineStr">
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G189" s="7" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="H189" s="7" t="inlineStr">
+      <c r="H192" s="7" t="inlineStr">
         <is>
           <t>**55%**</t>
         </is>
       </c>
-      <c r="I189" s="7" t="inlineStr">
+      <c r="I192" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="10" t="inlineStr">
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>`STI-401`</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
+      <c r="C193" s="8" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="D190" s="10" t="inlineStr">
+      <c r="D193" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E190" s="8" t="inlineStr">
+      <c r="E193" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F190" s="8" t="inlineStr">
+      <c r="F193" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G190" s="8" t="inlineStr">
+      <c r="G193" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H190" s="8" t="inlineStr">
+      <c r="H193" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I190" s="8" t="inlineStr">
+      <c r="I193" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="16" customHeight="1">
-      <c r="A191" s="9" t="inlineStr">
+    <row r="194" ht="16" customHeight="1">
+      <c r="A194" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t>`STI-402`</t>
         </is>
       </c>
-      <c r="C191" s="7" t="inlineStr">
+      <c r="C194" s="7" t="inlineStr">
         <is>
           <t>Data Warehouse &amp; BI</t>
         </is>
       </c>
-      <c r="D191" s="9" t="inlineStr">
+      <c r="D194" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="E194" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G191" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H191" s="7" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I191" s="7" t="inlineStr">
+      <c r="I194" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="10" t="inlineStr">
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="10" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>`STI-407`</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="C195" s="8" t="inlineStr">
         <is>
           <t>Web Back End Development</t>
         </is>
       </c>
-      <c r="D192" s="10" t="inlineStr">
+      <c r="D195" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E192" s="8" t="inlineStr">
+      <c r="E195" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F192" s="8" t="inlineStr">
+      <c r="F195" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G192" s="8" t="inlineStr">
+      <c r="G195" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H192" s="8" t="inlineStr">
+      <c r="H195" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I192" s="8" t="inlineStr">
+      <c r="I195" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="16" customHeight="1">
-      <c r="A193" s="9" t="inlineStr">
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B193" s="7" t="inlineStr">
+      <c r="B196" s="7" t="inlineStr">
         <is>
           <t>`STI-404`</t>
         </is>
       </c>
-      <c r="C193" s="7" t="inlineStr">
+      <c r="C196" s="7" t="inlineStr">
         <is>
           <t>Komputasi Awan (Cloud)</t>
         </is>
       </c>
-      <c r="D193" s="9" t="inlineStr">
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E193" s="7" t="inlineStr">
+      <c r="E196" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F196" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="H196" s="7" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I193" s="7" t="inlineStr">
+      <c r="I196" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="10" t="inlineStr">
+    <row r="197" ht="16" customHeight="1">
+      <c r="A197" s="10" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>`STI-405`</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C197" s="8" t="inlineStr">
         <is>
           <t>Dasar Keamanan Informasi</t>
         </is>
       </c>
-      <c r="D194" s="10" t="inlineStr">
+      <c r="D197" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E194" s="8" t="inlineStr">
+      <c r="E197" s="8" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F194" s="8" t="inlineStr">
+      <c r="F197" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G194" s="8" t="inlineStr">
+      <c r="G197" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="H194" s="8" t="inlineStr">
+      <c r="H197" s="8" t="inlineStr">
         <is>
           <t>**55%**</t>
         </is>
       </c>
-      <c r="I194" s="8" t="inlineStr">
+      <c r="I197" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="9" t="inlineStr">
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="9" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B198" s="7" t="inlineStr">
         <is>
           <t>`FST-408`</t>
         </is>
       </c>
-      <c r="C195" s="7" t="inlineStr">
+      <c r="C198" s="7" t="inlineStr">
         <is>
           <t>Probabilitas &amp; Statistika</t>
         </is>
       </c>
-      <c r="D195" s="9" t="inlineStr">
+      <c r="D198" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E195" s="7" t="inlineStr">
+      <c r="E198" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="F198" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="H195" s="7" t="inlineStr">
+      <c r="H198" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I195" s="7" t="inlineStr">
+      <c r="I198" s="7" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="16" customHeight="1">
-      <c r="A196" s="10" t="inlineStr">
+    <row r="199" ht="16" customHeight="1">
+      <c r="A199" s="10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>`STI-403`</t>
         </is>
       </c>
-      <c r="C196" s="8" t="inlineStr">
+      <c r="C199" s="8" t="inlineStr">
         <is>
           <t>Pengantar NLP &amp; IR</t>
         </is>
       </c>
-      <c r="D196" s="10" t="inlineStr">
+      <c r="D199" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E196" s="8" t="inlineStr">
+      <c r="E199" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F196" s="8" t="inlineStr">
+      <c r="F199" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G196" s="8" t="inlineStr">
+      <c r="G199" s="8" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H196" s="8" t="inlineStr">
+      <c r="H199" s="8" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I196" s="8" t="inlineStr">
+      <c r="I199" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="9" t="inlineStr">
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="9" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B200" s="7" t="inlineStr">
         <is>
           <t>`MKU-405`</t>
         </is>
       </c>
-      <c r="C197" s="7" t="inlineStr">
+      <c r="C200" s="7" t="inlineStr">
         <is>
           <t>Kewarganegaraan</t>
         </is>
       </c>
-      <c r="D197" s="9" t="inlineStr">
+      <c r="D200" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E197" s="7" t="inlineStr">
+      <c r="E200" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F197" s="7" t="inlineStr">
+      <c r="F200" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G197" s="7" t="inlineStr">
+      <c r="G200" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H197" s="7" t="inlineStr">
+      <c r="H200" s="7" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I197" s="7" t="inlineStr">
+      <c r="I200" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="10" t="inlineStr">
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="10" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>`STI-501`</t>
         </is>
       </c>
-      <c r="C198" s="8" t="inlineStr">
+      <c r="C201" s="8" t="inlineStr">
         <is>
           <t>Deep Learning &amp; Neural Net</t>
         </is>
       </c>
-      <c r="D198" s="10" t="inlineStr">
+      <c r="D201" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E198" s="8" t="inlineStr">
+      <c r="E201" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F198" s="8" t="inlineStr">
+      <c r="F201" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G198" s="8" t="inlineStr">
+      <c r="G201" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H198" s="8" t="inlineStr">
+      <c r="H201" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I198" s="8" t="inlineStr">
+      <c r="I201" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="9" t="inlineStr">
+    <row r="202" ht="16" customHeight="1">
+      <c r="A202" s="9" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B202" s="7" t="inlineStr">
         <is>
           <t>`STI-503`</t>
         </is>
       </c>
-      <c r="C199" s="7" t="inlineStr">
+      <c r="C202" s="7" t="inlineStr">
         <is>
           <t>Data Mining &amp; Visualisasi</t>
         </is>
       </c>
-      <c r="D199" s="9" t="inlineStr">
+      <c r="D202" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E199" s="7" t="inlineStr">
+      <c r="E202" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F199" s="7" t="inlineStr">
+      <c r="F202" s="7" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G199" s="7" t="inlineStr">
+      <c r="G202" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H199" s="7" t="inlineStr">
+      <c r="H202" s="7" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I199" s="7" t="inlineStr">
+      <c r="I202" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="10" t="inlineStr">
+    <row r="203" ht="16" customHeight="1">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>`STI-504`</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr">
+      <c r="C203" s="8" t="inlineStr">
         <is>
           <t>Internet of Things (IoT)</t>
         </is>
       </c>
-      <c r="D200" s="10" t="inlineStr">
+      <c r="D203" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E200" s="8" t="inlineStr">
+      <c r="E203" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr">
+      <c r="F203" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G200" s="8" t="inlineStr">
+      <c r="G203" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H200" s="8" t="inlineStr">
+      <c r="H203" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I200" s="8" t="inlineStr">
+      <c r="I203" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="16" customHeight="1">
-      <c r="A201" s="9" t="inlineStr">
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="9" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B204" s="7" t="inlineStr">
         <is>
           <t>`STI-505`</t>
         </is>
       </c>
-      <c r="C201" s="7" t="inlineStr">
+      <c r="C204" s="7" t="inlineStr">
         <is>
           <t>Pemrograman Mobile</t>
         </is>
       </c>
-      <c r="D201" s="9" t="inlineStr">
+      <c r="D204" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E201" s="7" t="inlineStr">
+      <c r="E204" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
+      <c r="F204" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G201" s="7" t="inlineStr">
+      <c r="G204" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H201" s="7" t="inlineStr">
+      <c r="H204" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I201" s="7" t="inlineStr">
+      <c r="I204" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="10" t="inlineStr">
+    <row r="205" ht="16" customHeight="1">
+      <c r="A205" s="10" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B205" s="8" t="inlineStr">
         <is>
           <t>`STI-506`</t>
         </is>
       </c>
-      <c r="C202" s="8" t="inlineStr">
+      <c r="C205" s="8" t="inlineStr">
         <is>
           <t>Manajemen Proyek TI</t>
         </is>
       </c>
-      <c r="D202" s="10" t="inlineStr">
+      <c r="D205" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E202" s="8" t="inlineStr">
+      <c r="E205" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F202" s="8" t="inlineStr">
+      <c r="F205" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G202" s="8" t="inlineStr">
+      <c r="G205" s="8" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H202" s="8" t="inlineStr">
+      <c r="H205" s="8" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I202" s="8" t="inlineStr">
+      <c r="I205" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="9" t="inlineStr">
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="9" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B203" s="7" t="inlineStr">
+      <c r="B206" s="7" t="inlineStr">
         <is>
           <t>`MKU-507`</t>
         </is>
       </c>
-      <c r="C203" s="7" t="inlineStr">
+      <c r="C206" s="7" t="inlineStr">
         <is>
           <t>KPM (Kuliah Pengabdian Kepada Masyarakat)</t>
         </is>
       </c>
-      <c r="D203" s="9" t="inlineStr">
+      <c r="D206" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E203" s="7" t="inlineStr">
+      <c r="E206" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
+      <c r="F206" s="7" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
+      <c r="G206" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="H203" s="7" t="inlineStr">
+      <c r="H206" s="7" t="inlineStr">
         <is>
           <t>**90%**</t>
         </is>
       </c>
-      <c r="I203" s="7" t="inlineStr">
+      <c r="I206" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="10" t="inlineStr">
+    <row r="207" ht="16" customHeight="1">
+      <c r="A207" s="10" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B204" s="8" t="inlineStr">
+      <c r="B207" s="8" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C204" s="8" t="inlineStr">
+      <c r="C207" s="8" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 1</t>
         </is>
       </c>
-      <c r="D204" s="10" t="inlineStr">
+      <c r="D207" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E204" s="8" t="inlineStr">
+      <c r="E207" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F204" s="8" t="inlineStr">
+      <c r="F207" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G204" s="8" t="inlineStr">
+      <c r="G207" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H204" s="8" t="inlineStr">
+      <c r="H207" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I204" s="8" t="inlineStr">
+      <c r="I207" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="16" customHeight="1">
-      <c r="A205" s="9" t="inlineStr">
+    <row r="208" ht="16" customHeight="1">
+      <c r="A208" s="9" t="inlineStr">
         <is>
           <t>38.B</t>
         </is>
       </c>
-      <c r="B205" s="7" t="inlineStr">
+      <c r="B208" s="7" t="inlineStr">
         <is>
           <t>`MKU-508`</t>
         </is>
       </c>
-      <c r="C205" s="7" t="inlineStr">
+      <c r="C208" s="7" t="inlineStr">
         <is>
           <t>Kewirausahaan II</t>
         </is>
       </c>
-      <c r="D205" s="9" t="inlineStr">
+      <c r="D208" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E205" s="7" t="inlineStr">
+      <c r="E208" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F205" s="7" t="inlineStr">
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G205" s="7" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H205" s="7" t="inlineStr">
+      <c r="H208" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I205" s="7" t="inlineStr">
+      <c r="I208" s="7" t="inlineStr">
         <is>
           <t>*MKWU 0 SKS (Sem 5)*</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="10" t="inlineStr">
+    <row r="209" ht="16" customHeight="1">
+      <c r="A209" s="10" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B206" s="8" t="inlineStr">
+      <c r="B209" s="8" t="inlineStr">
         <is>
           <t>`STI-601`</t>
         </is>
       </c>
-      <c r="C206" s="8" t="inlineStr">
+      <c r="C209" s="8" t="inlineStr">
         <is>
           <t>Integrasi Layanan Cerdas AI</t>
         </is>
       </c>
-      <c r="D206" s="10" t="inlineStr">
+      <c r="D209" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E206" s="8" t="inlineStr">
+      <c r="E209" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F206" s="8" t="inlineStr">
+      <c r="F209" s="8" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G206" s="8" t="inlineStr">
+      <c r="G209" s="8" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H206" s="8" t="inlineStr">
+      <c r="H209" s="8" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I206" s="8" t="inlineStr">
+      <c r="I209" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="16" customHeight="1">
-      <c r="A207" s="9" t="inlineStr">
+    <row r="210" ht="16" customHeight="1">
+      <c r="A210" s="9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="B210" s="7" t="inlineStr">
         <is>
           <t>`STI-602`</t>
         </is>
       </c>
-      <c r="C207" s="7" t="inlineStr">
+      <c r="C210" s="7" t="inlineStr">
         <is>
           <t>Smart City &amp; Pem. Digital</t>
         </is>
       </c>
-      <c r="D207" s="9" t="inlineStr">
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E207" s="7" t="inlineStr">
+      <c r="E210" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="F207" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G207" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H207" s="7" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I207" s="7" t="inlineStr">
+      <c r="I210" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="10" t="inlineStr">
+    <row r="211" ht="16" customHeight="1">
+      <c r="A211" s="10" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B208" s="8" t="inlineStr">
+      <c r="B211" s="8" t="inlineStr">
         <is>
           <t>`STI-603`</t>
         </is>
       </c>
-      <c r="C208" s="8" t="inlineStr">
+      <c r="C211" s="8" t="inlineStr">
         <is>
           <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
-      <c r="D208" s="10" t="inlineStr">
+      <c r="D211" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E208" s="8" t="inlineStr">
+      <c r="E211" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F208" s="8" t="inlineStr">
+      <c r="F211" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G208" s="8" t="inlineStr">
+      <c r="G211" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H208" s="8" t="inlineStr">
+      <c r="H211" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I208" s="8" t="inlineStr">
+      <c r="I211" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="9" t="inlineStr">
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="9" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t>`STI-604`</t>
         </is>
       </c>
-      <c r="C209" s="7" t="inlineStr">
+      <c r="C212" s="7" t="inlineStr">
         <is>
           <t>Digital Platform Engineering</t>
         </is>
       </c>
-      <c r="D209" s="9" t="inlineStr">
+      <c r="D212" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E209" s="7" t="inlineStr">
+      <c r="E212" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H209" s="7" t="inlineStr">
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I209" s="7" t="inlineStr">
+      <c r="I212" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="10" t="inlineStr">
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="10" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B210" s="8" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>`FST-611`</t>
         </is>
       </c>
-      <c r="C210" s="8" t="inlineStr">
+      <c r="C213" s="8" t="inlineStr">
         <is>
           <t>Metodologi Penelitian</t>
         </is>
       </c>
-      <c r="D210" s="10" t="inlineStr">
+      <c r="D213" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E210" s="8" t="inlineStr">
+      <c r="E213" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F210" s="8" t="inlineStr">
+      <c r="F213" s="8" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G210" s="8" t="inlineStr">
+      <c r="G213" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H210" s="8" t="inlineStr">
+      <c r="H213" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I210" s="8" t="inlineStr">
+      <c r="I213" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="9" t="inlineStr">
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="9" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C211" s="7" t="inlineStr">
+      <c r="C214" s="7" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 2</t>
         </is>
       </c>
-      <c r="D211" s="9" t="inlineStr">
+      <c r="D214" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E211" s="7" t="inlineStr">
+      <c r="E214" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F211" s="7" t="inlineStr">
+      <c r="F214" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H211" s="7" t="inlineStr">
+      <c r="H214" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I211" s="7" t="inlineStr">
+      <c r="I214" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="16" customHeight="1">
-      <c r="A212" s="10" t="inlineStr">
+    <row r="215" ht="16" customHeight="1">
+      <c r="A215" s="10" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="B212" s="8" t="inlineStr">
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C212" s="8" t="inlineStr">
+      <c r="C215" s="8" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 3</t>
         </is>
       </c>
-      <c r="D212" s="10" t="inlineStr">
+      <c r="D215" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E212" s="8" t="inlineStr">
+      <c r="E215" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F212" s="8" t="inlineStr">
+      <c r="F215" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G212" s="8" t="inlineStr">
+      <c r="G215" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H212" s="8" t="inlineStr">
+      <c r="H215" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I212" s="8" t="inlineStr">
+      <c r="I215" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="16" customHeight="1">
-      <c r="A213" s="9" t="inlineStr">
+    <row r="216" ht="16" customHeight="1">
+      <c r="A216" s="9" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>`STI-701`</t>
         </is>
       </c>
-      <c r="C213" s="7" t="inlineStr">
+      <c r="C216" s="7" t="inlineStr">
         <is>
           <t>Inovasi &amp; Startup Digital</t>
         </is>
       </c>
-      <c r="D213" s="9" t="inlineStr">
+      <c r="D216" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E213" s="7" t="inlineStr">
+      <c r="E216" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F213" s="7" t="inlineStr">
+      <c r="F216" s="7" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="G213" s="7" t="inlineStr">
+      <c r="G216" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="H213" s="7" t="inlineStr">
+      <c r="H216" s="7" t="inlineStr">
         <is>
           <t>**80%**</t>
         </is>
       </c>
-      <c r="I213" s="7" t="inlineStr">
+      <c r="I216" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="10" t="inlineStr">
+    <row r="217" ht="16" customHeight="1">
+      <c r="A217" s="10" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="B214" s="8" t="inlineStr">
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>`FST-610`</t>
         </is>
       </c>
-      <c r="C214" s="8" t="inlineStr">
+      <c r="C217" s="8" t="inlineStr">
         <is>
           <t>Capstone Project FSTI</t>
         </is>
       </c>
-      <c r="D214" s="10" t="inlineStr">
+      <c r="D217" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E214" s="8" t="inlineStr">
+      <c r="E217" s="8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F214" s="8" t="inlineStr">
+      <c r="F217" s="8" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="G214" s="8" t="inlineStr">
+      <c r="G217" s="8" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="H214" s="8" t="inlineStr">
+      <c r="H217" s="8" t="inlineStr">
         <is>
           <t>**85%**</t>
         </is>
       </c>
-      <c r="I214" s="8" t="inlineStr">
+      <c r="I217" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="9" t="inlineStr">
+    <row r="218" ht="16" customHeight="1">
+      <c r="A218" s="9" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="B215" s="7" t="inlineStr">
+      <c r="B218" s="7" t="inlineStr">
         <is>
           <t>`FST-612`</t>
         </is>
       </c>
-      <c r="C215" s="7" t="inlineStr">
+      <c r="C218" s="7" t="inlineStr">
         <is>
           <t>Praktik Kerja Lapangan(PKL)</t>
         </is>
       </c>
-      <c r="D215" s="9" t="inlineStr">
+      <c r="D218" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E215" s="7" t="inlineStr">
+      <c r="E218" s="7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F215" s="7" t="inlineStr">
+      <c r="F218" s="7" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="G215" s="7" t="inlineStr">
+      <c r="G218" s="7" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="H215" s="7" t="inlineStr">
+      <c r="H218" s="7" t="inlineStr">
         <is>
           <t>**85%**</t>
         </is>
       </c>
-      <c r="I215" s="7" t="inlineStr">
+      <c r="I218" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="16" customHeight="1">
-      <c r="A216" s="10" t="inlineStr">
+    <row r="219" ht="16" customHeight="1">
+      <c r="A219" s="10" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="B216" s="8" t="inlineStr">
+      <c r="B219" s="8" t="inlineStr">
         <is>
           <t>`FST-613`</t>
         </is>
       </c>
-      <c r="C216" s="8" t="inlineStr">
+      <c r="C219" s="8" t="inlineStr">
         <is>
           <t>Pra-Skripsi / Sempro</t>
         </is>
       </c>
-      <c r="D216" s="10" t="inlineStr">
+      <c r="D219" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E216" s="8" t="inlineStr">
+      <c r="E219" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F216" s="8" t="inlineStr">
+      <c r="F219" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G216" s="8" t="inlineStr">
+      <c r="G219" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="H216" s="8" t="inlineStr">
+      <c r="H219" s="8" t="inlineStr">
         <is>
           <t>**80%**</t>
         </is>
       </c>
-      <c r="I216" s="8" t="inlineStr">
+      <c r="I219" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="9" t="inlineStr">
+    <row r="220" ht="16" customHeight="1">
+      <c r="A220" s="9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="B217" s="7" t="inlineStr">
+      <c r="B220" s="7" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C217" s="7" t="inlineStr">
+      <c r="C220" s="7" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 4</t>
         </is>
       </c>
-      <c r="D217" s="9" t="inlineStr">
+      <c r="D220" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E217" s="7" t="inlineStr">
+      <c r="E220" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F217" s="7" t="inlineStr">
+      <c r="F220" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G217" s="7" t="inlineStr">
+      <c r="G220" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H217" s="7" t="inlineStr">
+      <c r="H220" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I217" s="7" t="inlineStr">
+      <c r="I220" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="16" customHeight="1">
-      <c r="A218" s="10" t="inlineStr">
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="10" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B218" s="8" t="inlineStr">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C218" s="8" t="inlineStr">
+      <c r="C221" s="8" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 5</t>
         </is>
       </c>
-      <c r="D218" s="10" t="inlineStr">
+      <c r="D221" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E218" s="8" t="inlineStr">
+      <c r="E221" s="8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F218" s="8" t="inlineStr">
+      <c r="F221" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G218" s="8" t="inlineStr">
+      <c r="G221" s="8" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H218" s="8" t="inlineStr">
+      <c r="H221" s="8" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I218" s="8" t="inlineStr">
+      <c r="I221" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="16" customHeight="1">
-      <c r="A219" s="9" t="inlineStr">
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="9" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B219" s="7" t="inlineStr">
+      <c r="B222" s="7" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C219" s="7" t="inlineStr">
+      <c r="C222" s="7" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 6</t>
         </is>
       </c>
-      <c r="D219" s="9" t="inlineStr">
+      <c r="D222" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E219" s="7" t="inlineStr">
+      <c r="E222" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F219" s="7" t="inlineStr">
+      <c r="F222" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G219" s="7" t="inlineStr">
+      <c r="G222" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H219" s="7" t="inlineStr">
+      <c r="H222" s="7" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I219" s="7" t="inlineStr">
+      <c r="I222" s="7" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="16" customHeight="1">
-      <c r="A220" s="10" t="inlineStr">
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="10" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B220" s="8" t="inlineStr">
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>`FST-714`</t>
         </is>
       </c>
-      <c r="C220" s="8" t="inlineStr">
+      <c r="C223" s="8" t="inlineStr">
         <is>
           <t>Skripsi / Tugas Akhir</t>
         </is>
       </c>
-      <c r="D220" s="10" t="inlineStr">
+      <c r="D223" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E220" s="8" t="inlineStr">
+      <c r="E223" s="8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F220" s="8" t="inlineStr">
+      <c r="F223" s="8" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="G220" s="8" t="inlineStr">
+      <c r="G223" s="8" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="H220" s="8" t="inlineStr">
+      <c r="H223" s="8" t="inlineStr">
         <is>
           <t>**90%**</t>
         </is>
       </c>
-      <c r="I220" s="8" t="inlineStr">
+      <c r="I223" s="8" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
@@ -9888,16 +9984,16 @@
     <mergeCell ref="A34:U34"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A165:I165"/>
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A150:F150"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A71:U71"/>
     <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A168:I168"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A148:F148"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
+++ b/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; Neural Net</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -3056,35 +3056,39 @@
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
-      <c r="K55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>**M**</t>
+        </is>
+      </c>
       <c r="L55" s="7" t="inlineStr"/>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>**R**</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>**R**</t>
-        </is>
-      </c>
-      <c r="O55" s="7" t="inlineStr"/>
-      <c r="P55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>**M**</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>**M**</t>
+        </is>
+      </c>
       <c r="Q55" s="7" t="inlineStr"/>
       <c r="R55" s="7" t="inlineStr"/>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>PL-1</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>PEO-1, PEO-3</t>
+          <t>PEO-1</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
-          <t>**R**</t>
+          <t>**M**</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3100,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -3155,7 +3159,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -3273,7 +3277,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3517,7 +3521,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3576,7 +3580,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -3635,12 +3639,12 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>Deep Learning &amp; Neural Net</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3654,39 +3658,35 @@
       <c r="H65" s="7" t="inlineStr"/>
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>**M**</t>
-        </is>
-      </c>
+      <c r="K65" s="7" t="inlineStr"/>
       <c r="L65" s="7" t="inlineStr"/>
-      <c r="M65" s="7" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr"/>
-      <c r="O65" s="7" t="inlineStr">
-        <is>
-          <t>**M**</t>
-        </is>
-      </c>
-      <c r="P65" s="7" t="inlineStr">
-        <is>
-          <t>**M**</t>
-        </is>
-      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>**R**</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>**R**</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr"/>
+      <c r="P65" s="7" t="inlineStr"/>
       <c r="Q65" s="7" t="inlineStr"/>
       <c r="R65" s="7" t="inlineStr"/>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>PL-1</t>
         </is>
       </c>
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>PEO-1</t>
+          <t>PEO-1, PEO-3</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
         <is>
-          <t>**M**</t>
+          <t>**R**</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>`FST-207`, `STI-402`, `STI-503`</t>
+          <t>`FST-207`, `STI-415`, `STI-520`</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>`STI-103`, `STI-307`, `STI-404`, `STI-305`</t>
+          <t>`STI-103`, `STI-312`, `STI-417`, `STI-310`</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>`STB-01`, `STB-02`, `STI-504`</t>
+          <t>`STB-01`, `STB-02`, `STI-521`</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>`STI-301`, `STI-604`</t>
+          <t>`STI-306`, `STI-627`</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>`STI-506`, `STB-03`</t>
+          <t>`STI-523`, `STB-03`</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-603`, `STB-01`, `STB-03`</t>
+          <t>`STI-418`, `STI-519`, `STB-01`, `STB-03`</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`, `STI-304`</t>
+          <t>`STI-306`, `STI-309`</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>`STI-506`, `STC-06`</t>
+          <t>`STI-523`, `STC-06`</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`, `STI-602`</t>
+          <t>`STI-306`, `STI-625`</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>`STI-102`, `STI-201`, `STI-202`, `FST-408`</t>
+          <t>`STI-102`, `STI-204`, `STI-205`, `FST-408`</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`</t>
+          <t>`STI-311`, `STI-416`</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+          <t>`STI-311`, `STI-416`, `STI-522`, `STI-627`</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>`STI-402`, `STI-503`, `STA-01`</t>
+          <t>`STI-415`, `STI-520`, `STA-01`</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>`STI-401`, `STA-04`</t>
+          <t>`STI-413`, `STA-04`</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>`MKU-204`, `STI-701`, `FST-610`</t>
+          <t>`MKU-204`, `STI-728`, `FST-610`</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-403`, `STI-601`, `STA-03`, `STA-05`</t>
+          <t>`STI-307`, `STI-414`, `STI-624`, `STA-03`, `STA-05`</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>`STI-401`, `STA-06`</t>
+          <t>`STI-413`, `STA-06`</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>`STI-303`, `STC-01`</t>
+          <t>`STI-308`, `STC-01`</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-505`</t>
+          <t>`STI-311`, `STI-522`</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>`STI-401`, `STI-501`, `STA-04`</t>
+          <t>`STI-413`, `STI-626`, `STA-04`</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`, `STB-02`</t>
+          <t>`STI-417`, `STB-02`</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>`STI-604`, `STC-05`</t>
+          <t>`STI-627`, `STC-05`</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-602`, `STB-04`</t>
+          <t>`STI-418`, `STI-625`, `STB-04`</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
+          <t>`STI-307`, `STI-413`, `STI-414`, `STI-626`, `STI-624`</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`, `STI-504`, `STB-01`</t>
+          <t>`STI-417`, `STI-521`, `STB-01`</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+          <t>`STI-311`, `STI-416`, `STI-522`, `STI-627`</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`, `STB-02`</t>
+          <t>`STI-417`, `STB-02`</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>`STI-305`, `STC-05`</t>
+          <t>`STI-310`, `STC-05`</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-603`, `STB-01`</t>
+          <t>`STI-418`, `STI-519`, `STB-01`</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>`STI-601`, `STI-604`, `FST-610`</t>
+          <t>`STI-624`, `STI-627`, `FST-610`</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>`STI-402`, `STI-503`</t>
+          <t>`STI-415`, `STI-520`</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>`STI-303`, `STC-01`</t>
+          <t>`STI-308`, `STC-01`</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`, `STC-04`</t>
+          <t>`STI-311`, `STC-04`</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>`STI-304`, `STI-407`, `STI-604`</t>
+          <t>`STI-309`, `STI-416`, `STI-627`</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>`MKU-204`, `STI-701`, `FST-610`</t>
+          <t>`MKU-204`, `STI-728`, `FST-610`</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>`STI-504`, `STA-06`</t>
+          <t>`STI-521`, `STA-06`</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>`STI-305`, `STI-307`</t>
+          <t>`STI-310`, `STI-312`</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="C187" s="8" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="B194" s="7" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; Neural Net</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="G201" s="8" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B202" s="7" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="B204" s="7" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B210" s="7" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>Deep Learning &amp; Neural Net</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G211" s="8" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="B212" s="7" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="B216" s="7" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">

--- a/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
+++ b/KURIKULUM2026_REVISI/004_MATRIKS_KETERLACAKAN_OBE_VMTS_PEO_PL_CPL_MK.xlsx
@@ -4790,9 +4790,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>`STA-01`</t>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -4837,9 +4837,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -4884,9 +4884,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>`STA-03`</t>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>`STA-602`</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -4931,9 +4931,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>`STA-04`</t>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>`STA-701`</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -4978,9 +4978,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>`STA-05`</t>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>`STA-702`</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -5025,9 +5025,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>`STA-06`</t>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>`STA-703`</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -5135,9 +5135,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>`STB-01`</t>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -5182,9 +5182,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>`STB-02`</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>`STB-601`</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -5229,9 +5229,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>`STB-602`</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -5276,9 +5276,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>`STB-04`</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -5323,9 +5323,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>`STB-05`</t>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>`STB-702`</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5370,9 +5370,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t>`STB-06`</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>`STB-703`</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -5480,9 +5480,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>`STC-01`</t>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>`STC-501`</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
@@ -5527,9 +5527,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>`STC-02`</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>`STC-601`</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -5574,9 +5574,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>`STC-03`</t>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>`STC-602`</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
@@ -5621,9 +5621,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -5668,9 +5668,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>`STC-05`</t>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>`STC-702`</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5715,9 +5715,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B107" s="10" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>`STC-703`</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>`STA-01`, `STA-04`</t>
+          <t>`STA-501`, `STA-701`</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>`STB-01`, `STB-02`, `STI-521`</t>
+          <t>`STB-501`, `STB-601`, `STI-521`</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
@@ -6286,9 +6286,9 @@
           <t>*Enterprise Architecture*</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>`STB-06`</t>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>`STB-703`</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>`STB-04`, `STB-05`</t>
+          <t>`STB-701`, `STB-702`</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>`STI-523`, `STB-03`</t>
+          <t>`STI-523`, `STB-602`</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>`STI-418`, `STI-519`, `STB-01`, `STB-03`</t>
+          <t>`STI-418`, `STI-519`, `STB-501`, `STB-602`</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>`FST-610`, `STC-02`</t>
+          <t>`FST-610`, `STC-601`</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>`STI-523`, `STC-06`</t>
+          <t>`STI-523`, `STC-703`</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
@@ -6446,9 +6446,9 @@
           <t>*Business Process Management*</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
-        <is>
-          <t>`STC-02`</t>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>`STC-601`</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
@@ -6483,9 +6483,9 @@
           <t>`STI-102`, `STI-204`, `STI-205`, `FST-408`</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>`STC-03`, `STC-05`</t>
+          <t>`STC-602`, `STC-702`</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>`STI-415`, `STI-520`, `STA-01`</t>
+          <t>`STI-415`, `STI-520`, `STA-501`</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>`STI-413`, `STA-04`</t>
+          <t>`STI-413`, `STA-701`</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>`STB-04`, `STB-03`</t>
+          <t>`STB-701`, `STB-602`</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>`FST-206`, `STB-05`</t>
+          <t>`FST-206`, `STB-702`</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -6643,9 +6643,9 @@
           <t>`MKU-204`, `STI-728`, `FST-610`</t>
         </is>
       </c>
-      <c r="D142" s="9" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>`STC-703`</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-414`, `STI-624`, `STA-03`, `STA-05`</t>
+          <t>`STI-307`, `STI-414`, `STI-624`, `STA-602`, `STA-702`</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>`STI-413`, `STA-06`</t>
+          <t>`STI-413`, `STA-703`</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>`STI-308`, `STC-01`</t>
+          <t>`STI-308`, `STC-501`</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-626`, `STA-04`</t>
+          <t>`STI-413`, `STI-626`, `STA-701`</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>`STA-02`, `STA-06`</t>
+          <t>`STA-601`, `STA-703`</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>`STI-417`, `STB-02`</t>
+          <t>`STI-417`, `STB-601`</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`, `STC-05`</t>
+          <t>`STI-627`, `STC-702`</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>`STI-418`, `STI-625`, `STB-04`</t>
+          <t>`STI-418`, `STI-625`, `STB-701`</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>`STA-03..06`</t>
+          <t>`STA-602, STA-701..703`</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>`STI-417`, `STI-521`, `STB-01`</t>
+          <t>`STI-417`, `STI-521`, `STB-501`</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>`STC-03..05`</t>
+          <t>`STC-602, STC-701..702`</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>`STI-417`, `STB-02`</t>
+          <t>`STI-417`, `STB-601`</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>`STI-310`, `STC-05`</t>
+          <t>`STI-310`, `STC-702`</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>`STI-418`, `STI-519`, `STB-01`</t>
-        </is>
-      </c>
-      <c r="D157" s="10" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+          <t>`STI-418`, `STI-519`, `STB-501`</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>`STB-602`</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>`STB-06`, `STC-02`</t>
+          <t>`STB-703`, `STC-601`</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>`STB-04`, `STB-05`</t>
+          <t>`STB-701`, `STB-702`</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>`STA-01`, `STA-04`</t>
+          <t>`STA-501`, `STA-701`</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>`STI-308`, `STC-01`</t>
+          <t>`STI-308`, `STC-501`</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>`STI-311`, `STC-04`</t>
+          <t>`STI-311`, `STC-701`</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>`FST-205`, `STC-05`</t>
+          <t>`FST-205`, `STC-702`</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>`STB-03`, `STB-04`</t>
+          <t>`STB-602`, `STB-701`</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
@@ -7296,9 +7296,9 @@
           <t>`MKU-204`, `STI-728`, `FST-610`</t>
         </is>
       </c>
-      <c r="D164" s="9" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>`STC-703`</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>`STI-521`, `STA-06`</t>
+          <t>`STI-521`, `STA-703`</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
